--- a/artfynd/A 36315-2024 artfynd.xlsx
+++ b/artfynd/A 36315-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84665358</v>
+        <v>84665565</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509707.9196227886</v>
+        <v>509722</v>
       </c>
       <c r="R2" t="n">
-        <v>6750654.901616241</v>
+        <v>6750653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +754,9 @@
           <t>2020-04-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,11 +768,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Grov låga av gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84665429</v>
+        <v>84626816</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,20 +812,28 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen, Dlr</t>
+          <t>Hästhagarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509714.7768559629</v>
+        <v>509660</v>
       </c>
       <c r="R3" t="n">
-        <v>6750643.238260365</v>
+        <v>6750567</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,22 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar på tre olika lågor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,6 +883,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Grova lågor i rasbrant mot mycket liten bäck</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -909,6 +900,213 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>84665429</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hästhagen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>509715</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6750643</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-04-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-04-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Billbäck</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Billbäck</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>84665358</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hästhagen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>509708</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6750655</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-04-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-04-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Grov låga av gran</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Billbäck</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Billbäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36315-2024 artfynd.xlsx
+++ b/artfynd/A 36315-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84665565</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84626816</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84665429</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,8 +1127,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84665358</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>